--- a/Analysis/Prompt_Ablation/prompt_ablation_bootstrap_ci.xlsx
+++ b/Analysis/Prompt_Ablation/prompt_ablation_bootstrap_ci.xlsx
@@ -470,13 +470,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1402870661856997</v>
+        <v>0.129115869197204</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06110443180819265</v>
+        <v>0.04970693986770326</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2175898068044959</v>
+        <v>0.2045980639614213</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1433833942562333</v>
+        <v>0.1469780034108743</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07275155195442486</v>
+        <v>0.07925996354973402</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2153767613129721</v>
+        <v>0.2160481983652852</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -594,13 +594,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.3948717948717949</v>
+        <v>0.3943589743589744</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3446153846153847</v>
+        <v>0.3471794871794873</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4451282051282052</v>
+        <v>0.442051282051282</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -656,13 +656,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.4492307692307692</v>
+        <v>0.4581196581196582</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4</v>
+        <v>0.4109401709401709</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4994871794871795</v>
+        <v>0.5051282051282051</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.066596720576085</v>
+        <v>0.05271646724718222</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.004423977349486356</v>
+        <v>-0.01008005877709469</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1375659752205001</v>
+        <v>0.1155032425411017</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.1077436329102537</v>
+        <v>0.09950595942880783</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0418846149395514</v>
+        <v>0.03615995389219989</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1713296055207489</v>
+        <v>0.1601715306870428</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -842,13 +842,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.3466666666666666</v>
+        <v>0.3441025641025641</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3046153846153846</v>
+        <v>0.3071794871794872</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3897435897435897</v>
+        <v>0.382051282051282</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.365897435897436</v>
+        <v>0.3680911680911682</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3207692307692308</v>
+        <v>0.3261538461538462</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4107692307692308</v>
+        <v>0.4076923076923077</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.05257401577674884</v>
+        <v>-0.05215995956934628</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1060075534065187</v>
+        <v>-0.1006801340484112</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0004031379416731174</v>
+        <v>-0.003750941815790188</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.02737419351683122</v>
+        <v>0.02447314788363281</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.02631458085789206</v>
+        <v>-0.02108499365697549</v>
       </c>
       <c r="F20" t="n">
-        <v>0.08042457051349264</v>
+        <v>0.07064614147218956</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1090,13 +1090,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.2865811965811966</v>
+        <v>0.2885470085470086</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2486324786324786</v>
+        <v>0.2536168091168091</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3253846153846154</v>
+        <v>0.3235049857549858</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1155,10 +1155,10 @@
         <v>0.3712820512820513</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3323076923076924</v>
+        <v>0.337948717948718</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4112820512820513</v>
+        <v>0.4051282051282051</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>

--- a/Analysis/Prompt_Ablation/prompt_ablation_bootstrap_ci.xlsx
+++ b/Analysis/Prompt_Ablation/prompt_ablation_bootstrap_ci.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,10 +473,10 @@
         <v>0.129115869197204</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04970693986770326</v>
+        <v>0.05020324358478531</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2045980639614213</v>
+        <v>0.2062761576589543</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,10 +504,10 @@
         <v>0.1611965811965812</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06864805505045335</v>
+        <v>0.06794699991367575</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2538495639272271</v>
+        <v>0.2529582111982419</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -535,10 +535,10 @@
         <v>0.1469780034108743</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07925996354973402</v>
+        <v>0.07874280177782245</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2160481983652852</v>
+        <v>0.2149966270808549</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -566,10 +566,10 @@
         <v>0.166624789172893</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08148885754855113</v>
+        <v>0.08366652602997068</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2518287508755649</v>
+        <v>0.2512937905689058</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -597,10 +597,10 @@
         <v>0.3943589743589744</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3471794871794873</v>
+        <v>0.3487179487179487</v>
       </c>
       <c r="F6" t="n">
-        <v>0.442051282051282</v>
+        <v>0.441025641025641</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -628,10 +628,10 @@
         <v>0.3630769230769231</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3056410256410256</v>
+        <v>0.3046153846153846</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4215641025641023</v>
+        <v>0.4235897435897436</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -659,10 +659,10 @@
         <v>0.4581196581196582</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4109401709401709</v>
+        <v>0.4099145299145299</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5051282051282051</v>
+        <v>0.5056410256410256</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -690,10 +690,10 @@
         <v>0.4123076923076923</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3558717948717948</v>
+        <v>0.3569230769230769</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4707692307692307</v>
+        <v>0.4687179487179488</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.05271646724718222</v>
+        <v>0.1881205303542168</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.01008005877709469</v>
+        <v>0.1005698299409952</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1155032425411017</v>
+        <v>0.275899318396181</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.03925880845638263</v>
+        <v>0.2113384498493255</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.03051890368127127</v>
+        <v>0.1184545539840438</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1075430499038108</v>
+        <v>0.3044735012770429</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.09950595942880783</v>
+        <v>0.1262396069841691</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03615995389219989</v>
+        <v>0.02595470669926883</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1601715306870428</v>
+        <v>0.2249589800551877</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -811,13 +811,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9.022331875086455e-05</v>
+        <v>0.1775216582662204</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.06322805649227897</v>
+        <v>0.09196734571908829</v>
       </c>
       <c r="F13" t="n">
-        <v>0.06389847916338091</v>
+        <v>0.2621097011469292</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -842,13 +842,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.3441025641025641</v>
+        <v>0.3521367521367521</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3071794871794872</v>
+        <v>0.2905982905982906</v>
       </c>
       <c r="F14" t="n">
-        <v>0.382051282051282</v>
+        <v>0.4153846153846154</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -873,13 +873,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.3271794871794871</v>
+        <v>0.3675213675213675</v>
       </c>
       <c r="E15" t="n">
-        <v>0.282051282051282</v>
+        <v>0.305982905982906</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3723333333333331</v>
+        <v>0.429059829059829</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.3680911680911682</v>
+        <v>0.3606837606837607</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3261538461538462</v>
+        <v>0.2974358974358974</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4076923076923077</v>
+        <v>0.4256410256410256</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.32</v>
+        <v>0.3504273504273504</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2769230769230769</v>
+        <v>0.2905982905982906</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3651282051282052</v>
+        <v>0.411965811965812</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.05215995956934628</v>
+        <v>0.05271646724718222</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1006801340484112</v>
+        <v>-0.01036815747608856</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.003750941815790188</v>
+        <v>0.1133508715719367</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.09595441595441596</v>
+        <v>0.03925880845638263</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02009569886013001</v>
+        <v>-0.02847690045893089</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1728101458678704</v>
+        <v>0.1073813913097417</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.02447314788363281</v>
+        <v>0.09950595942880783</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.02108499365697549</v>
+        <v>0.03576730546721489</v>
       </c>
       <c r="F20" t="n">
-        <v>0.07064614147218956</v>
+        <v>0.1612123733961786</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.01493740916077781</v>
+        <v>9.022331875086455e-05</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.03989074513525549</v>
+        <v>-0.06459345113170778</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0694271174272395</v>
+        <v>0.06287317282437196</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1090,13 +1090,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.2885470085470086</v>
+        <v>0.3441025641025641</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2536168091168091</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3235049857549858</v>
+        <v>0.3830769230769231</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1121,13 +1121,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.3357264957264957</v>
+        <v>0.3271794871794871</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2887179487179487</v>
+        <v>0.2820512820512821</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3846175213675214</v>
+        <v>0.3733333333333333</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1152,13 +1152,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.3712820512820513</v>
+        <v>0.3680911680911682</v>
       </c>
       <c r="E24" t="n">
-        <v>0.337948717948718</v>
+        <v>0.3282051282051282</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4051282051282051</v>
+        <v>0.4101424501424502</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1183,13 +1183,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.3292307692307692</v>
+        <v>0.32</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2902564102564102</v>
+        <v>0.2769230769230769</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3702564102564102</v>
+        <v>0.3641025641025641</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1200,12 +1200,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1214,13 +1214,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.3043558774812271</v>
+        <v>-0.05215995956934628</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2336548749900678</v>
+        <v>-0.09967669924677901</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3720861091640698</v>
+        <v>-0.004760934750196345</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1231,12 +1231,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1245,13 +1245,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.1797599859730369</v>
+        <v>0.09595441595441596</v>
       </c>
       <c r="E27" t="n">
-        <v>0.08938357751450335</v>
+        <v>0.0213990799260598</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2697936506664896</v>
+        <v>0.1720128131700218</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1262,27 +1262,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>scale_0_10</t>
+          <t>no_anchors</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.2448104830132161</v>
+        <v>0.02447314788363281</v>
       </c>
       <c r="E28" t="n">
-        <v>0.175284761372638</v>
+        <v>-0.02082980469703219</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3117432646359379</v>
+        <v>0.07004910320542866</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1293,58 +1293,58 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>scale_0_10</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.5517948717948717</v>
+        <v>0.01493740916077781</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5005128205128205</v>
+        <v>-0.04072418478332118</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6030769230769231</v>
+        <v>0.06979803709401429</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>top1</t>
+          <t>kendall_tau</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>cot_scaffold</t>
+          <t>control</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.3666666666666666</v>
+        <v>0.2885470085470086</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3087179487179487</v>
+        <v>0.2545562678062678</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4241025641025641</v>
+        <v>0.3238190883190883</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1355,27 +1355,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>scale_0_10</t>
+          <t>cot_scaffold</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.477948717948718</v>
+        <v>0.3357264957264957</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4266666666666667</v>
+        <v>0.2883739316239317</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5271794871794871</v>
+        <v>0.3846175213675214</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1386,62 +1386,62 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>no_anchors</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.2619994766592649</v>
+        <v>0.3712820512820513</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1943913787179963</v>
+        <v>0.3384615384615385</v>
       </c>
       <c r="F32" t="n">
-        <v>0.328700680253943</v>
+        <v>0.4051282051282051</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>top1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>cot_scaffold</t>
+          <t>scale_0_10</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2054972818323348</v>
+        <v>0.3292307692307692</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1289602161250411</v>
+        <v>0.2892307692307692</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2811501873969109</v>
+        <v>0.3692307692307693</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>top1</t>
         </is>
       </c>
     </row>
@@ -1453,22 +1453,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>scale_0_10</t>
+          <t>control</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.2610929704125466</v>
+        <v>0.3043558774812271</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1950406024737455</v>
+        <v>0.2327453421339375</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3261719604183354</v>
+        <v>0.373981856208468</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1484,26 +1484,26 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>cot_scaffold</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.4543589743589743</v>
+        <v>0.1797599859730369</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4020512820512821</v>
+        <v>0.0898605919535231</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5046153846153847</v>
+        <v>0.2707856181873195</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>top1</t>
+          <t>kendall_tau</t>
         </is>
       </c>
     </row>
@@ -1515,26 +1515,26 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>cot_scaffold</t>
+          <t>scale_0_10</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.4426495726495726</v>
+        <v>0.2448104830132161</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3914508547008547</v>
+        <v>0.174932234495815</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4941025641025641</v>
+        <v>0.3133036231999569</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>top1</t>
+          <t>kendall_tau</t>
         </is>
       </c>
     </row>
@@ -1546,22 +1546,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>scale_0_10</t>
+          <t>control</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.4892307692307692</v>
+        <v>0.5517948717948717</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4389743589743589</v>
+        <v>0.5005128205128205</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5394871794871795</v>
+        <v>0.6041025641025641</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1577,26 +1577,26 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>cot_scaffold</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.2051161113291622</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1491282124710038</v>
+        <v>0.3087179487179487</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2608277735056178</v>
+        <v>0.4246153846153847</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>top1</t>
         </is>
       </c>
     </row>
@@ -1608,26 +1608,26 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>cot_scaffold</t>
+          <t>scale_0_10</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.1957489388554643</v>
+        <v>0.477948717948718</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1174920140696772</v>
+        <v>0.4256410256410256</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2744808287741222</v>
+        <v>0.5271794871794873</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>top1</t>
         </is>
       </c>
     </row>
@@ -1639,22 +1639,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>scale_0_10</t>
+          <t>control</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.1011253708109534</v>
+        <v>0.3265215998205405</v>
       </c>
       <c r="E40" t="n">
-        <v>0.04639652027368129</v>
+        <v>0.2344118186445994</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1557448740867242</v>
+        <v>0.4169795408337659</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1670,26 +1670,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>cot_scaffold</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.4738461538461539</v>
+        <v>0.2436026802521506</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4276923076923077</v>
+        <v>0.1548120274098037</v>
       </c>
       <c r="F41" t="n">
-        <v>0.517948717948718</v>
+        <v>0.331866688999114</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>top1</t>
+          <t>kendall_tau</t>
         </is>
       </c>
     </row>
@@ -1701,26 +1701,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>cot_scaffold</t>
+          <t>scale_0_10</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.4000854700854701</v>
+        <v>0.2511986164105515</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3492286324786326</v>
+        <v>0.1577498839245908</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4514551282051282</v>
+        <v>0.3425681436208484</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>top1</t>
+          <t>kendall_tau</t>
         </is>
       </c>
     </row>
@@ -1732,24 +1732,458 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.4769230769230769</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.4136752136752136</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.5452991452991454</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>top1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>cot_scaffold</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.4094017094017094</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.3461538461538461</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.4726709401709399</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>top1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>scale_0_10</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.4170940170940171</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.3504273504273505</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.4837606837606838</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>top1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.2619994766592649</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.1937594410489697</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.3284809130604586</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>cot_scaffold</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.2054972818323348</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.1295700607716085</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.2814267352016062</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>scale_0_10</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.2610929704125466</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.1965082809325003</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.3266161127977218</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.4543589743589743</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.403051282051282</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.5056410256410256</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>top1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>cot_scaffold</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.4426495726495726</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.3923931623931625</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.4951282051282051</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>top1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>scale_0_10</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.4892307692307692</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.4400000000000001</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>top1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>qwen</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0.2051161113291622</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.1493162481275977</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.2601185124662541</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>cot_scaffold</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.1957489388554643</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.114660058688921</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.2712706915395846</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
         <is>
           <t>scale_0_10</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D54" t="n">
+        <v>0.1011253708109534</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.04609580319455476</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.1574688581782485</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.4738461538461539</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.4287179487179487</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.517948717948718</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>top1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>cot_scaffold</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.4000854700854701</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.3487179487179487</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.4513675213675213</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>top1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>scale_0_10</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
         <v>0.4071794871794872</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E57" t="n">
         <v>0.3661538461538462</v>
       </c>
-      <c r="F43" t="n">
-        <v>0.4471794871794872</v>
-      </c>
-      <c r="G43" t="inlineStr">
+      <c r="F57" t="n">
+        <v>0.4492307692307692</v>
+      </c>
+      <c r="G57" t="inlineStr">
         <is>
           <t>top1</t>
         </is>
